--- a/exports/export_excel_sample.xlsx
+++ b/exports/export_excel_sample.xlsx
@@ -410,7 +410,7 @@
         <v>2026-01 구독자수</v>
       </c>
       <c r="D1" t="str">
-        <v>2026-02 구독자수2026-02 구독자수2026-02 구독자수2026-02 구독자수2026-02 구독자수</v>
+        <v>2026-02 구독자수</v>
       </c>
       <c r="E1" t="str">
         <v>2026-03 구독자수</v>
